--- a/membership_forms/005_membership_crm_intake_form--membership_forms.xlsx
+++ b/membership_forms/005_membership_crm_intake_form--membership_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -753,12 +753,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'member'}</t>
+          <t>member</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Member'}</t>
+          <t>Member</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'associate'}</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Associate'}</t>
+          <t>Associate</t>
         </is>
       </c>
     </row>
@@ -820,46 +820,46 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'member'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Member'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>membership_crm_intake_form_page_6_choices</t>
+          <t>membership_crm_intake_form_page_7_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'associate'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Associate'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>membership_crm_intake_form_page_6_choices</t>
+          <t>membership_crm_intake_form_page_7_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'active'}</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Active'}</t>
+          <t>Suspended</t>
         </is>
       </c>
     </row>
@@ -888,46 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'pending'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Pending'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>membership_crm_intake_form_page_7_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'suspended'}</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'Suspended'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>membership_crm_intake_form_page_7_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'id':_4,_'label':_'cancelled'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'id': 4, 'label': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
